--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/119.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/119.xlsx
@@ -426,13 +426,13 @@
         <v>-16.9161968220759</v>
       </c>
       <c r="E2">
-        <v>-22.71210046367857</v>
+        <v>-18.86207356556251</v>
       </c>
       <c r="F2">
-        <v>-2.95078483011042</v>
+        <v>-1.875527493110938</v>
       </c>
       <c r="G2">
-        <v>-17.46163569967365</v>
+        <v>-18.77870804711537</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.30134213295816</v>
       </c>
       <c r="E3">
-        <v>-22.83794276682087</v>
+        <v>-20.06328195777472</v>
       </c>
       <c r="F3">
-        <v>-3.198633185395435</v>
+        <v>-1.838790227164183</v>
       </c>
       <c r="G3">
-        <v>-17.78058122876389</v>
+        <v>-18.48486221652409</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.65690995716766</v>
       </c>
       <c r="E4">
-        <v>-22.97633192137548</v>
+        <v>-19.69079704689614</v>
       </c>
       <c r="F4">
-        <v>-2.596670190924673</v>
+        <v>-1.881289616764812</v>
       </c>
       <c r="G4">
-        <v>-16.96357090030401</v>
+        <v>-17.76194834461711</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.9263590590507</v>
       </c>
       <c r="E5">
-        <v>-23.03746719207696</v>
+        <v>-20.82163342642046</v>
       </c>
       <c r="F5">
-        <v>-1.718787126622827</v>
+        <v>-1.703508718245593</v>
       </c>
       <c r="G5">
-        <v>-16.45503179363483</v>
+        <v>-17.6669433489465</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.09302274998235</v>
       </c>
       <c r="E6">
-        <v>-23.05551289528334</v>
+        <v>-21.14815059435583</v>
       </c>
       <c r="F6">
-        <v>-1.965636470820066</v>
+        <v>-1.611374382236621</v>
       </c>
       <c r="G6">
-        <v>-17.39256192465427</v>
+        <v>-17.17201666457538</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.14686940801702</v>
       </c>
       <c r="E7">
-        <v>-25.39240031142461</v>
+        <v>-22.28225139798146</v>
       </c>
       <c r="F7">
-        <v>-2.839665969964089</v>
+        <v>-1.432926647958149</v>
       </c>
       <c r="G7">
-        <v>-16.89859207817579</v>
+        <v>-17.12416432696487</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.08841732768932</v>
       </c>
       <c r="E8">
-        <v>-23.97723923781386</v>
+        <v>-22.10721015348524</v>
       </c>
       <c r="F8">
-        <v>-1.989343517520785</v>
+        <v>-1.18705974750063</v>
       </c>
       <c r="G8">
-        <v>-16.82108690349941</v>
+        <v>-17.00481674872671</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.91334767082677</v>
       </c>
       <c r="E9">
-        <v>-23.07188900753714</v>
+        <v>-22.32066860273613</v>
       </c>
       <c r="F9">
-        <v>-2.020664917388037</v>
+        <v>-1.099031628707335</v>
       </c>
       <c r="G9">
-        <v>-16.27913418218087</v>
+        <v>-16.46401144965596</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.64777952850047</v>
       </c>
       <c r="E10">
-        <v>-25.0748250074716</v>
+        <v>-23.99466611253284</v>
       </c>
       <c r="F10">
-        <v>-2.185764339337798</v>
+        <v>-1.266255813045277</v>
       </c>
       <c r="G10">
-        <v>-16.34972218906309</v>
+        <v>-15.48950534299258</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.29445388278926</v>
       </c>
       <c r="E11">
-        <v>-23.90755665820589</v>
+        <v>-23.93596462366772</v>
       </c>
       <c r="F11">
-        <v>-1.424240387372393</v>
+        <v>-0.9469516572273738</v>
       </c>
       <c r="G11">
-        <v>-15.29317082287939</v>
+        <v>-15.41274553589697</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.90922944822487</v>
       </c>
       <c r="E12">
-        <v>-27.59219852815595</v>
+        <v>-23.93985202946775</v>
       </c>
       <c r="F12">
-        <v>-1.201301868256962</v>
+        <v>-1.018847320851148</v>
       </c>
       <c r="G12">
-        <v>-15.17265232569212</v>
+        <v>-15.22798183581158</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.50875639809026</v>
       </c>
       <c r="E13">
-        <v>-28.31504211658007</v>
+        <v>-25.69302220674968</v>
       </c>
       <c r="F13">
-        <v>-1.38697130955304</v>
+        <v>-0.9050602893003999</v>
       </c>
       <c r="G13">
-        <v>-14.9324925415002</v>
+        <v>-14.80772114137401</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.14869338410299</v>
       </c>
       <c r="E14">
-        <v>-29.88985678672856</v>
+        <v>-26.21822900446485</v>
       </c>
       <c r="F14">
-        <v>-1.000494012674723</v>
+        <v>-0.5316239804443549</v>
       </c>
       <c r="G14">
-        <v>-13.55732329467244</v>
+        <v>-13.91104916320549</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.83827177034477</v>
       </c>
       <c r="E15">
-        <v>-28.79282754738835</v>
+        <v>-27.38657303546369</v>
       </c>
       <c r="F15">
-        <v>-0.7168601855887691</v>
+        <v>-0.253631335371466</v>
       </c>
       <c r="G15">
-        <v>-13.25466228496927</v>
+        <v>-13.66006653731111</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.59131832767985</v>
       </c>
       <c r="E16">
-        <v>-30.95563518745509</v>
+        <v>-28.51230927148112</v>
       </c>
       <c r="F16">
-        <v>-0.6531164855759444</v>
+        <v>-0.1653447659484975</v>
       </c>
       <c r="G16">
-        <v>-13.99301348964349</v>
+        <v>-13.74621066583948</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.39675260850379</v>
       </c>
       <c r="E17">
-        <v>-30.1519763364668</v>
+        <v>-29.59141740395469</v>
       </c>
       <c r="F17">
-        <v>-1.128629196009361</v>
+        <v>0.03072068625271471</v>
       </c>
       <c r="G17">
-        <v>-13.50164655552236</v>
+        <v>-13.31458670556909</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.2288730131982</v>
       </c>
       <c r="E18">
-        <v>-31.73037730459427</v>
+        <v>-29.78815502441182</v>
       </c>
       <c r="F18">
-        <v>-0.2272370648160653</v>
+        <v>0.5832798488205138</v>
       </c>
       <c r="G18">
-        <v>-13.43381941104523</v>
+        <v>-12.8744112513905</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.07152218059422</v>
       </c>
       <c r="E19">
-        <v>-32.79808902519252</v>
+        <v>-30.74686571378994</v>
       </c>
       <c r="F19">
-        <v>-0.6942921440668994</v>
+        <v>0.7237138029845167</v>
       </c>
       <c r="G19">
-        <v>-12.30136586736409</v>
+        <v>-12.57933314935222</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.88331000748008</v>
       </c>
       <c r="E20">
-        <v>-33.01366768882473</v>
+        <v>-31.22476328130399</v>
       </c>
       <c r="F20">
-        <v>0.1278798989270687</v>
+        <v>0.740643975962933</v>
       </c>
       <c r="G20">
-        <v>-12.89279350405653</v>
+        <v>-12.68464536466855</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.66062683876312</v>
       </c>
       <c r="E21">
-        <v>-34.89089221177363</v>
+        <v>-31.97288539045667</v>
       </c>
       <c r="F21">
-        <v>-0.0681176271471139</v>
+        <v>0.6018361070106255</v>
       </c>
       <c r="G21">
-        <v>-13.83122825807679</v>
+        <v>-12.18554932118542</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.36780717698725</v>
       </c>
       <c r="E22">
-        <v>-35.0125480779005</v>
+        <v>-31.62194318671999</v>
       </c>
       <c r="F22">
-        <v>-0.08858989913990088</v>
+        <v>0.980509354587169</v>
       </c>
       <c r="G22">
-        <v>-12.26288479746338</v>
+        <v>-12.67016748053853</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.01901157816883</v>
       </c>
       <c r="E23">
-        <v>-34.42116608754117</v>
+        <v>-32.75184509369622</v>
       </c>
       <c r="F23">
-        <v>0.05117556253004291</v>
+        <v>1.405743477140267</v>
       </c>
       <c r="G23">
-        <v>-12.42115205069355</v>
+        <v>-12.38703222963229</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.60926771922751</v>
       </c>
       <c r="E24">
-        <v>-36.19000425454602</v>
+        <v>-32.43852890795682</v>
       </c>
       <c r="F24">
-        <v>0.2680877087901075</v>
+        <v>0.9748482917564373</v>
       </c>
       <c r="G24">
-        <v>-12.55654787593328</v>
+        <v>-11.90495171402175</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.16182925224818</v>
       </c>
       <c r="E25">
-        <v>-36.9005294181807</v>
+        <v>-33.54131865140456</v>
       </c>
       <c r="F25">
-        <v>-0.3111821606809616</v>
+        <v>1.183010393140731</v>
       </c>
       <c r="G25">
-        <v>-12.37887495815736</v>
+        <v>-11.8950648242552</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.69382631872206</v>
       </c>
       <c r="E26">
-        <v>-34.68035969990108</v>
+        <v>-32.77553916430436</v>
       </c>
       <c r="F26">
-        <v>-0.07612545482997672</v>
+        <v>1.068566466239562</v>
       </c>
       <c r="G26">
-        <v>-12.30291664965121</v>
+        <v>-12.41330545782496</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.22335713918244</v>
       </c>
       <c r="E27">
-        <v>-36.87757669579403</v>
+        <v>-33.14806768390185</v>
       </c>
       <c r="F27">
-        <v>-0.06574186943588492</v>
+        <v>0.9094022967308595</v>
       </c>
       <c r="G27">
-        <v>-12.76492837158987</v>
+        <v>-12.14591821829232</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.78180554971</v>
       </c>
       <c r="E28">
-        <v>-35.20470055305502</v>
+        <v>-32.91879172932035</v>
       </c>
       <c r="F28">
-        <v>0.4233949996713756</v>
+        <v>1.156187856638083</v>
       </c>
       <c r="G28">
-        <v>-10.87803882580866</v>
+        <v>-11.92022065376287</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.38017632891425</v>
       </c>
       <c r="E29">
-        <v>-34.80137181827261</v>
+        <v>-33.45751722989783</v>
       </c>
       <c r="F29">
-        <v>-0.1760795791213763</v>
+        <v>0.895798847242086</v>
       </c>
       <c r="G29">
-        <v>-11.59718669864295</v>
+        <v>-11.21879712595765</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.05791585077405</v>
       </c>
       <c r="E30">
-        <v>-34.09373313650868</v>
+        <v>-32.80111671624832</v>
       </c>
       <c r="F30">
-        <v>-0.3327859825459727</v>
+        <v>0.8663536995421748</v>
       </c>
       <c r="G30">
-        <v>-12.51981078341943</v>
+        <v>-12.25498729507526</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.814355114141</v>
       </c>
       <c r="E31">
-        <v>-35.06178024494502</v>
+        <v>-32.37231841301639</v>
       </c>
       <c r="F31">
-        <v>-1.05816080942061</v>
+        <v>0.8884909900145888</v>
       </c>
       <c r="G31">
-        <v>-12.43308184810265</v>
+        <v>-11.53729099623363</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.67923389008003</v>
       </c>
       <c r="E32">
-        <v>-34.95588996900719</v>
+        <v>-32.2262541239335</v>
       </c>
       <c r="F32">
-        <v>-0.4468107555413247</v>
+        <v>0.6285940308558551</v>
       </c>
       <c r="G32">
-        <v>-11.58635210858983</v>
+        <v>-11.82388548372309</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.6426403543495</v>
       </c>
       <c r="E33">
-        <v>-35.11641366331747</v>
+        <v>-31.52864129430771</v>
       </c>
       <c r="F33">
-        <v>-0.183261524503648</v>
+        <v>0.6994360111432688</v>
       </c>
       <c r="G33">
-        <v>-12.08654727554581</v>
+        <v>-12.00100753439028</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.70914312026983</v>
       </c>
       <c r="E34">
-        <v>-34.53838009415615</v>
+        <v>-31.11965173248956</v>
       </c>
       <c r="F34">
-        <v>-0.2592990251414202</v>
+        <v>0.7413331776420622</v>
       </c>
       <c r="G34">
-        <v>-12.35482738972862</v>
+        <v>-11.63856047355062</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.8645768660726</v>
       </c>
       <c r="E35">
-        <v>-33.70909800589932</v>
+        <v>-30.9737348824087</v>
       </c>
       <c r="F35">
-        <v>-0.4831570320739586</v>
+        <v>0.5130036434692121</v>
       </c>
       <c r="G35">
-        <v>-11.16303031611917</v>
+        <v>-11.89299319842215</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.09135552243863</v>
       </c>
       <c r="E36">
-        <v>-34.10826106972294</v>
+        <v>-30.56365717922344</v>
       </c>
       <c r="F36">
-        <v>-0.2424011584917131</v>
+        <v>1.06027782200715</v>
       </c>
       <c r="G36">
-        <v>-11.41954902591901</v>
+        <v>-11.32133803589051</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.37844136482648</v>
       </c>
       <c r="E37">
-        <v>-33.74084722987197</v>
+        <v>-30.24976369710989</v>
       </c>
       <c r="F37">
-        <v>0.2251285752809251</v>
+        <v>0.7074396969891177</v>
       </c>
       <c r="G37">
-        <v>-11.68285045016656</v>
+        <v>-11.34464676359997</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.69525493728714</v>
       </c>
       <c r="E38">
-        <v>-31.53892879875931</v>
+        <v>-29.3792962887504</v>
       </c>
       <c r="F38">
-        <v>0.4947704485661922</v>
+        <v>0.7760368016149447</v>
       </c>
       <c r="G38">
-        <v>-10.80836066341643</v>
+        <v>-11.92466544642924</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.04174540944059</v>
       </c>
       <c r="E39">
-        <v>-31.84411092011904</v>
+        <v>-29.88964081973966</v>
       </c>
       <c r="F39">
-        <v>-0.2627259810868017</v>
+        <v>0.9707197086208845</v>
       </c>
       <c r="G39">
-        <v>-12.56396761206122</v>
+        <v>-12.45249403950987</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.38737536212841</v>
       </c>
       <c r="E40">
-        <v>-30.44948332329824</v>
+        <v>-28.115671360143</v>
       </c>
       <c r="F40">
-        <v>0.4067406730380915</v>
+        <v>0.8559924800679586</v>
       </c>
       <c r="G40">
-        <v>-12.93796982846116</v>
+        <v>-12.23521612628676</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.7419950456947</v>
       </c>
       <c r="E41">
-        <v>-32.12036384799568</v>
+        <v>-28.65328172347977</v>
       </c>
       <c r="F41">
-        <v>0.3379298496223422</v>
+        <v>1.389525700128259</v>
       </c>
       <c r="G41">
-        <v>-12.86469536539468</v>
+        <v>-12.53260865340506</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.08726914962577</v>
       </c>
       <c r="E42">
-        <v>-31.13630818650779</v>
+        <v>-28.33580194338722</v>
       </c>
       <c r="F42">
-        <v>-0.2587962061279209</v>
+        <v>1.314538569357236</v>
       </c>
       <c r="G42">
-        <v>-11.96166752951909</v>
+        <v>-12.40313530227028</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.42942172902228</v>
       </c>
       <c r="E43">
-        <v>-29.63691998722951</v>
+        <v>-26.78196514364045</v>
       </c>
       <c r="F43">
-        <v>0.3974985779250574</v>
+        <v>1.247772156691596</v>
       </c>
       <c r="G43">
-        <v>-12.51467283806412</v>
+        <v>-12.59614112302981</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.76081997302732</v>
       </c>
       <c r="E44">
-        <v>-29.41945576565583</v>
+        <v>-27.11994102162102</v>
       </c>
       <c r="F44">
-        <v>-0.3867350663880961</v>
+        <v>1.369664763278738</v>
       </c>
       <c r="G44">
-        <v>-12.49693021782291</v>
+        <v>-13.03485456023737</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.07770601291442</v>
       </c>
       <c r="E45">
-        <v>-29.80399952561604</v>
+        <v>-26.3974234602859</v>
       </c>
       <c r="F45">
-        <v>0.7121837571049504</v>
+        <v>1.220979441415449</v>
       </c>
       <c r="G45">
-        <v>-12.44104461910554</v>
+        <v>-13.09184189317219</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.3838801001932</v>
       </c>
       <c r="E46">
-        <v>-28.12550408795453</v>
+        <v>-25.43385351365773</v>
       </c>
       <c r="F46">
-        <v>0.3511456231666055</v>
+        <v>1.242871535136634</v>
       </c>
       <c r="G46">
-        <v>-12.60149184406929</v>
+        <v>-12.57050361114507</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.66627129874851</v>
       </c>
       <c r="E47">
-        <v>-29.39683945338647</v>
+        <v>-24.57720383937594</v>
       </c>
       <c r="F47">
-        <v>0.6327996521598682</v>
+        <v>1.442032596322108</v>
       </c>
       <c r="G47">
-        <v>-13.45485940170502</v>
+        <v>-13.28246018800315</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.93953969737757</v>
       </c>
       <c r="E48">
-        <v>-28.79162934592113</v>
+        <v>-25.16900738068474</v>
       </c>
       <c r="F48">
-        <v>-0.1191475442617718</v>
+        <v>1.006944215145307</v>
       </c>
       <c r="G48">
-        <v>-13.9997100495197</v>
+        <v>-13.20642877864845</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-15.18336580842775</v>
       </c>
       <c r="E49">
-        <v>-27.87789793519091</v>
+        <v>-23.84107620452936</v>
       </c>
       <c r="F49">
-        <v>0.5609404367018167</v>
+        <v>0.8893607757875283</v>
       </c>
       <c r="G49">
-        <v>-13.37667804417954</v>
+        <v>-13.62603026007677</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.4152520631279</v>
       </c>
       <c r="E50">
-        <v>-26.9804305000087</v>
+        <v>-22.77527080792921</v>
       </c>
       <c r="F50">
-        <v>0.2901181398675603</v>
+        <v>1.461413080078005</v>
       </c>
       <c r="G50">
-        <v>-12.5142655619079</v>
+        <v>-13.10029809490281</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-15.61842370144691</v>
       </c>
       <c r="E51">
-        <v>-26.00832155089669</v>
+        <v>-23.19315447179948</v>
       </c>
       <c r="F51">
-        <v>0.4915696369217749</v>
+        <v>1.308786386112196</v>
       </c>
       <c r="G51">
-        <v>-13.37465341174913</v>
+        <v>-13.53407591946087</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-15.804014723097</v>
       </c>
       <c r="E52">
-        <v>-25.6919548314392</v>
+        <v>-22.8372450273183</v>
       </c>
       <c r="F52">
-        <v>0.428297277961143</v>
+        <v>1.361589837836248</v>
       </c>
       <c r="G52">
-        <v>-13.70506402571124</v>
+        <v>-13.46999127735511</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.96664499091029</v>
       </c>
       <c r="E53">
-        <v>-24.7206183796336</v>
+        <v>-22.37892985120082</v>
       </c>
       <c r="F53">
-        <v>0.2585407744728431</v>
+        <v>1.122196628631608</v>
       </c>
       <c r="G53">
-        <v>-13.64623611783969</v>
+        <v>-13.79146270183725</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-16.10748323773044</v>
       </c>
       <c r="E54">
-        <v>-23.46717504858902</v>
+        <v>-20.80724670239125</v>
       </c>
       <c r="F54">
-        <v>0.003305038689662275</v>
+        <v>1.203736145558774</v>
       </c>
       <c r="G54">
-        <v>-14.21743962155707</v>
+        <v>-13.77946894118568</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-16.23405523747138</v>
       </c>
       <c r="E55">
-        <v>-24.66668477736938</v>
+        <v>-20.47058739240065</v>
       </c>
       <c r="F55">
-        <v>0.06110271748519218</v>
+        <v>1.157422124068254</v>
       </c>
       <c r="G55">
-        <v>-14.36009331676009</v>
+        <v>-14.62547811519135</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-16.33623276199771</v>
       </c>
       <c r="E56">
-        <v>-24.01898316483971</v>
+        <v>-21.39675351783742</v>
       </c>
       <c r="F56">
-        <v>-0.3320338249442308</v>
+        <v>1.296402293440344</v>
       </c>
       <c r="G56">
-        <v>-13.9864592153475</v>
+        <v>-13.78677380455161</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-16.43196114915628</v>
       </c>
       <c r="E57">
-        <v>-24.90543628358847</v>
+        <v>-20.03445451796908</v>
       </c>
       <c r="F57">
-        <v>-0.04964337732987932</v>
+        <v>0.7173602250050445</v>
       </c>
       <c r="G57">
-        <v>-13.24163075334273</v>
+        <v>-14.29773829294594</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-16.50079028399064</v>
       </c>
       <c r="E58">
-        <v>-24.16341524187195</v>
+        <v>-19.75505553251389</v>
       </c>
       <c r="F58">
-        <v>0.1836190847266419</v>
+        <v>1.040806217836945</v>
       </c>
       <c r="G58">
-        <v>-14.42618562145642</v>
+        <v>-13.65740357782818</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-16.56338389227442</v>
       </c>
       <c r="E59">
-        <v>-22.93654831009495</v>
+        <v>-19.36307544767658</v>
       </c>
       <c r="F59">
-        <v>0.3174940257952784</v>
+        <v>1.267124475955798</v>
       </c>
       <c r="G59">
-        <v>-14.63372806809926</v>
+        <v>-14.67544515592066</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.60134484683194</v>
       </c>
       <c r="E60">
-        <v>-22.88303002896321</v>
+        <v>-19.59845869951123</v>
       </c>
       <c r="F60">
-        <v>0.497671391210796</v>
+        <v>1.312013705513503</v>
       </c>
       <c r="G60">
-        <v>-13.92137596343564</v>
+        <v>-14.61127696998799</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.62745074594415</v>
       </c>
       <c r="E61">
-        <v>-22.681125813618</v>
+        <v>-18.52699247587534</v>
       </c>
       <c r="F61">
-        <v>-0.2168973828943219</v>
+        <v>1.158875080492764</v>
       </c>
       <c r="G61">
-        <v>-14.22312712864881</v>
+        <v>-14.33105139392855</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.63412555796335</v>
       </c>
       <c r="E62">
-        <v>-22.61881933732292</v>
+        <v>-18.9156832173434</v>
       </c>
       <c r="F62">
-        <v>-0.3305319948429553</v>
+        <v>0.9496211908715811</v>
       </c>
       <c r="G62">
-        <v>-14.65292748382231</v>
+        <v>-14.46242667249796</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.62077222335195</v>
       </c>
       <c r="E63">
-        <v>-23.50353226052657</v>
+        <v>-18.30386119744893</v>
       </c>
       <c r="F63">
-        <v>0.1236113217004429</v>
+        <v>0.9214020269278131</v>
       </c>
       <c r="G63">
-        <v>-14.35398939590607</v>
+        <v>-15.63307410417479</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.58975445978871</v>
       </c>
       <c r="E64">
-        <v>-20.68455253343317</v>
+        <v>-18.12551399673814</v>
       </c>
       <c r="F64">
-        <v>-0.4328966682765014</v>
+        <v>1.190783792848601</v>
       </c>
       <c r="G64">
-        <v>-14.6466434215915</v>
+        <v>-14.75320748893927</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.52782172928865</v>
       </c>
       <c r="E65">
-        <v>-22.50024100078774</v>
+        <v>-16.92004440970666</v>
       </c>
       <c r="F65">
-        <v>0.0449793743571026</v>
+        <v>0.9402092804409731</v>
       </c>
       <c r="G65">
-        <v>-14.37016034790342</v>
+        <v>-15.24094287733417</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-16.45027091792393</v>
       </c>
       <c r="E66">
-        <v>-22.57726230480668</v>
+        <v>-18.07077882468823</v>
       </c>
       <c r="F66">
-        <v>-0.265278181054827</v>
+        <v>0.8538188440030127</v>
       </c>
       <c r="G66">
-        <v>-14.14604619996848</v>
+        <v>-15.00627218364506</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.33695919258557</v>
       </c>
       <c r="E67">
-        <v>-22.19563202259084</v>
+        <v>-17.3870356442817</v>
       </c>
       <c r="F67">
-        <v>0.446460061634925</v>
+        <v>0.7964080127845902</v>
       </c>
       <c r="G67">
-        <v>-15.2192214823361</v>
+        <v>-15.30223532809973</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.20962763326931</v>
       </c>
       <c r="E68">
-        <v>-21.32531828305037</v>
+        <v>-18.32010025372901</v>
       </c>
       <c r="F68">
-        <v>-0.4305051715846192</v>
+        <v>0.7557103222850504</v>
       </c>
       <c r="G68">
-        <v>-15.24979330149804</v>
+        <v>-15.33909643098166</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-16.05025096245084</v>
       </c>
       <c r="E69">
-        <v>-20.17378229828311</v>
+        <v>-17.4361805938884</v>
       </c>
       <c r="F69">
-        <v>0.3313053955021545</v>
+        <v>1.062986583414305</v>
       </c>
       <c r="G69">
-        <v>-14.13073418294161</v>
+        <v>-15.2619685088987</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.87365732018762</v>
       </c>
       <c r="E70">
-        <v>-20.97880755579727</v>
+        <v>-17.3428413225742</v>
       </c>
       <c r="F70">
-        <v>-0.5813061437946581</v>
+        <v>0.8941040075359582</v>
       </c>
       <c r="G70">
-        <v>-14.63950956199628</v>
+        <v>-15.20621214203859</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.67396874775811</v>
       </c>
       <c r="E71">
-        <v>-19.97755136960761</v>
+        <v>-17.60380004974715</v>
       </c>
       <c r="F71">
-        <v>0.5856912263300631</v>
+        <v>0.7774350857908703</v>
       </c>
       <c r="G71">
-        <v>-14.11577200568994</v>
+        <v>-15.14953157159322</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.4569919297609</v>
       </c>
       <c r="E72">
-        <v>-21.21609713163003</v>
+        <v>-17.68307239430415</v>
       </c>
       <c r="F72">
-        <v>-0.2992412445696068</v>
+        <v>0.5271637558526668</v>
       </c>
       <c r="G72">
-        <v>-14.95785723057516</v>
+        <v>-15.23907097346234</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.23180494903463</v>
       </c>
       <c r="E73">
-        <v>-21.99463320731444</v>
+        <v>-17.50373257608673</v>
       </c>
       <c r="F73">
-        <v>-0.3121124172743055</v>
+        <v>0.7444412121373659</v>
       </c>
       <c r="G73">
-        <v>-14.73013111749842</v>
+        <v>-14.87881041121773</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.99455272959737</v>
       </c>
       <c r="E74">
-        <v>-22.16330342563837</v>
+        <v>-18.5014253069597</v>
       </c>
       <c r="F74">
-        <v>-0.6049568615119867</v>
+        <v>0.6987352123205004</v>
       </c>
       <c r="G74">
-        <v>-14.73995534939478</v>
+        <v>-15.08598474287323</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.76584773000317</v>
       </c>
       <c r="E75">
-        <v>-22.06343115291022</v>
+        <v>-18.64354819849533</v>
       </c>
       <c r="F75">
-        <v>0.1877476678621946</v>
+        <v>0.8855420020606225</v>
       </c>
       <c r="G75">
-        <v>-14.20754489955675</v>
+        <v>-14.80644318189666</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.531696473575</v>
       </c>
       <c r="E76">
-        <v>-21.57486813871401</v>
+        <v>-18.28353122801389</v>
       </c>
       <c r="F76">
-        <v>-0.5430695328488356</v>
+        <v>0.6654911717113506</v>
       </c>
       <c r="G76">
-        <v>-15.44882341540156</v>
+        <v>-14.11235062490328</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.31784258870442</v>
       </c>
       <c r="E77">
-        <v>-22.82365571986346</v>
+        <v>-18.33222763079751</v>
       </c>
       <c r="F77">
-        <v>-0.5765148667368657</v>
+        <v>0.8563138866202448</v>
       </c>
       <c r="G77">
-        <v>-14.5097438074673</v>
+        <v>-14.58454947223646</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.11036423037742</v>
       </c>
       <c r="E78">
-        <v>-23.08775842800931</v>
+        <v>-18.91565829807545</v>
       </c>
       <c r="F78">
-        <v>0.06450647914329535</v>
+        <v>0.5033498497569866</v>
       </c>
       <c r="G78">
-        <v>-14.24291265653256</v>
+        <v>-14.18400903706786</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.92675862601874</v>
       </c>
       <c r="E79">
-        <v>-23.90105272927121</v>
+        <v>-19.80898913477812</v>
       </c>
       <c r="F79">
-        <v>-0.8282201006493151</v>
+        <v>0.1819590364514317</v>
       </c>
       <c r="G79">
-        <v>-13.52706737560603</v>
+        <v>-13.70244675425865</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.75950454577424</v>
       </c>
       <c r="E80">
-        <v>-23.61884201974911</v>
+        <v>-19.62589896673438</v>
       </c>
       <c r="F80">
-        <v>-1.087313543427333</v>
+        <v>0.5380402198514244</v>
       </c>
       <c r="G80">
-        <v>-13.8938600208176</v>
+        <v>-14.072771736902</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.61116749031064</v>
       </c>
       <c r="E81">
-        <v>-24.87929181829867</v>
+        <v>-19.8147745581536</v>
       </c>
       <c r="F81">
-        <v>-0.5308859050884606</v>
+        <v>0.796772494441822</v>
       </c>
       <c r="G81">
-        <v>-13.95498930004622</v>
+        <v>-13.5191724839625</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.482631655678</v>
       </c>
       <c r="E82">
-        <v>-24.79692117809335</v>
+        <v>-20.15393410136175</v>
       </c>
       <c r="F82">
-        <v>-0.7082816127653775</v>
+        <v>0.6520741048882071</v>
       </c>
       <c r="G82">
-        <v>-13.56644784701838</v>
+        <v>-13.73928044432238</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.36309526487229</v>
       </c>
       <c r="E83">
-        <v>-24.0702504054334</v>
+        <v>-21.16583912138828</v>
       </c>
       <c r="F83">
-        <v>-0.6785912683142376</v>
+        <v>0.6246957338582806</v>
       </c>
       <c r="G83">
-        <v>-14.85468582582355</v>
+        <v>-13.08791402793486</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.26152367492189</v>
       </c>
       <c r="E84">
-        <v>-25.16128656083188</v>
+        <v>-22.15807037936909</v>
       </c>
       <c r="F84">
-        <v>-0.1858617697810356</v>
+        <v>0.5034873587458514</v>
       </c>
       <c r="G84">
-        <v>-14.24382380639486</v>
+        <v>-13.4350621254706</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.15569209883216</v>
       </c>
       <c r="E85">
-        <v>-27.27565322061149</v>
+        <v>-23.75387953276458</v>
       </c>
       <c r="F85">
-        <v>-0.4462176444809202</v>
+        <v>0.7258973794582962</v>
       </c>
       <c r="G85">
-        <v>-13.69068926599257</v>
+        <v>-12.65239353136223</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.05937629088605</v>
       </c>
       <c r="E86">
-        <v>-27.65768636432584</v>
+        <v>-25.36951611702481</v>
       </c>
       <c r="F86">
-        <v>-0.6052898652079121</v>
+        <v>0.6090412466801756</v>
       </c>
       <c r="G86">
-        <v>-13.85105947399089</v>
+        <v>-12.33028116908297</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.95048586539368</v>
       </c>
       <c r="E87">
-        <v>-26.64159906049522</v>
+        <v>-24.55046961807802</v>
       </c>
       <c r="F87">
-        <v>-0.6226466473987702</v>
+        <v>0.2461020095524058</v>
       </c>
       <c r="G87">
-        <v>-13.88179707543436</v>
+        <v>-12.57228544432851</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.84029120776166</v>
       </c>
       <c r="E88">
-        <v>-31.12010235591831</v>
+        <v>-26.52797965828188</v>
       </c>
       <c r="F88">
-        <v>-0.7857704130928543</v>
+        <v>0.4365395336189981</v>
       </c>
       <c r="G88">
-        <v>-12.74717139225342</v>
+        <v>-12.77666366852693</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.72015427996892</v>
       </c>
       <c r="E89">
-        <v>-30.49831678205557</v>
+        <v>-27.00369263663907</v>
       </c>
       <c r="F89">
-        <v>0.1122278968511721</v>
+        <v>0.1706261420137316</v>
       </c>
       <c r="G89">
-        <v>-13.04938204851462</v>
+        <v>-12.18879969820136</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.59706319154832</v>
       </c>
       <c r="E90">
-        <v>-31.83036794384518</v>
+        <v>-28.85878261983229</v>
       </c>
       <c r="F90">
-        <v>-0.6563040433419168</v>
+        <v>0.1333429819485315</v>
       </c>
       <c r="G90">
-        <v>-13.12887530519713</v>
+        <v>-12.29293968919627</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.47762725249737</v>
       </c>
       <c r="E91">
-        <v>-32.639147704397</v>
+        <v>-30.17079661358526</v>
       </c>
       <c r="F91">
-        <v>-0.5748763560141282</v>
+        <v>-0.08380856249094214</v>
       </c>
       <c r="G91">
-        <v>-13.87133712723007</v>
+        <v>-12.75135641583297</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.36161143545812</v>
       </c>
       <c r="E92">
-        <v>-34.46452353716673</v>
+        <v>-31.6605784350692</v>
       </c>
       <c r="F92">
-        <v>-0.9761706606263207</v>
+        <v>-0.1071743218217078</v>
       </c>
       <c r="G92">
-        <v>-12.7012588378741</v>
+        <v>-12.34189767714113</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.26613555137992</v>
       </c>
       <c r="E93">
-        <v>-34.9489499528834</v>
+        <v>-33.16847656435205</v>
       </c>
       <c r="F93">
-        <v>-1.015515627157089</v>
+        <v>-0.1062838268636983</v>
       </c>
       <c r="G93">
-        <v>-13.45494555627652</v>
+        <v>-12.43664812521411</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.17931708983106</v>
       </c>
       <c r="E94">
-        <v>-37.86545331170076</v>
+        <v>-34.99314635119656</v>
       </c>
       <c r="F94">
-        <v>-0.4853091305864317</v>
+        <v>-0.0600683810941111</v>
       </c>
       <c r="G94">
-        <v>-12.76184899834465</v>
+        <v>-12.29817423210146</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.12225595601168</v>
       </c>
       <c r="E95">
-        <v>-39.64191885130365</v>
+        <v>-36.82512371336711</v>
       </c>
       <c r="F95">
-        <v>-0.4742852171899759</v>
+        <v>-0.1465424826397543</v>
       </c>
       <c r="G95">
-        <v>-13.23768069677637</v>
+        <v>-12.89885695836939</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.08193202171882</v>
       </c>
       <c r="E96">
-        <v>-41.14664392713433</v>
+        <v>-38.47539600347074</v>
       </c>
       <c r="F96">
-        <v>-1.197352212480414</v>
+        <v>-0.1023432831285811</v>
       </c>
       <c r="G96">
-        <v>-13.51774701741575</v>
+        <v>-12.70077976624163</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.07439436973695</v>
       </c>
       <c r="E97">
-        <v>-44.15787372984838</v>
+        <v>-40.85797497400212</v>
       </c>
       <c r="F97">
-        <v>-1.518680069863356</v>
+        <v>-0.7577525424279667</v>
       </c>
       <c r="G97">
-        <v>-14.15248168538558</v>
+        <v>-13.30226007498215</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.09399478816922</v>
       </c>
       <c r="E98">
-        <v>-45.80781480134885</v>
+        <v>-42.97266350765941</v>
       </c>
       <c r="F98">
-        <v>-1.840224959505832</v>
+        <v>-0.4303428115736705</v>
       </c>
       <c r="G98">
-        <v>-12.56728717380882</v>
+        <v>-13.08438691199227</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.1384238705535</v>
       </c>
       <c r="E99">
-        <v>-46.4004084911122</v>
+        <v>-44.42130154115394</v>
       </c>
       <c r="F99">
-        <v>-1.809597731522126</v>
+        <v>-0.8408319943569376</v>
       </c>
       <c r="G99">
-        <v>-13.30559791194189</v>
+        <v>-13.49770433118978</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.20896802415978</v>
       </c>
       <c r="E100">
-        <v>-49.22856266202214</v>
+        <v>-47.04759510543758</v>
       </c>
       <c r="F100">
-        <v>-1.835035237727293</v>
+        <v>-0.7067309089873368</v>
       </c>
       <c r="G100">
-        <v>-13.97055586467074</v>
+        <v>-13.31424078191077</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.28048911360404</v>
       </c>
       <c r="E101">
-        <v>-50.21305544900196</v>
+        <v>-48.88923491375534</v>
       </c>
       <c r="F101">
-        <v>-1.775031616538108</v>
+        <v>-0.8589649568042187</v>
       </c>
       <c r="G101">
-        <v>-13.82365318264568</v>
+        <v>-13.18131080493735</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.3723690118607</v>
       </c>
       <c r="E102">
-        <v>-52.15874254573216</v>
+        <v>-51.32504663213987</v>
       </c>
       <c r="F102">
-        <v>-1.456233593203315</v>
+        <v>-0.9884172443093087</v>
       </c>
       <c r="G102">
-        <v>-13.29798236996961</v>
+        <v>-13.96070421995617</v>
       </c>
     </row>
   </sheetData>
